--- a/consulting_forms/016_weight_loss_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/016_weight_loss_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'heart_conditions'}</t>
+          <t>heart_conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Heart Conditions'}</t>
+          <t>Heart Conditions</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_conditions'}</t>
+          <t>other_conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other Conditions'}</t>
+          <t>Other Conditions</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'medication_1'}</t>
+          <t>medication_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Medication 1'}</t>
+          <t>Medication 1</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medication_2'}</t>
+          <t>medication_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medication 2'}</t>
+          <t>Medication 2</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medication_3'}</t>
+          <t>medication_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medication 3'}</t>
+          <t>Medication 3</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'family_history'}</t>
+          <t>family_history</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Family History'}</t>
+          <t>Family History</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'past_procedures'}</t>
+          <t>past_procedures</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Past Procedures'}</t>
+          <t>Past Procedures</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_history'}</t>
+          <t>other_history</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other History'}</t>
+          <t>Other History</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less Than 10'}</t>
+          <t>Less Than 10</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'more_than_5'}</t>
+          <t>more_than_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'More Than 5'}</t>
+          <t>More Than 5</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_month'}</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less Than 1 Month'}</t>
+          <t>Less Than 1 Month</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1-3 Months'}</t>
+          <t>1-3 Months</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_3_months'}</t>
+          <t>more_than_3_months</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More Than 3 Months'}</t>
+          <t>More Than 3 Months</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-5_times_a_week'}</t>
+          <t>3-5_times_a_week</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-5 Times A Week'}</t>
+          <t>3-5 Times A Week</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
